--- a/inputs/location_code_crosswalk_CalSim.xlsx
+++ b/inputs/location_code_crosswalk_CalSim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\calsim_gits\eis-appendix-generation\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/fnufferrodriguez_usbr_gov/Documents/Desktop/eis-appendix-generation/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE2C0AE-041C-44F6-87C0-BC10225BA465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{9BE2C0AE-041C-44F6-87C0-BC10225BA465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65FD36E7-F64C-4C54-913F-39C68A09D1D8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{14B88182-57F4-4B3C-8644-9F1A6EE53B53}"/>
+    <workbookView xWindow="-33075" yWindow="840" windowWidth="27015" windowHeight="19365" xr2:uid="{14B88182-57F4-4B3C-8644-9F1A6EE53B53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="561">
   <si>
     <t>QueryID</t>
   </si>
@@ -909,13 +909,823 @@
   </si>
   <si>
     <t>S_SLUIS</t>
+  </si>
+  <si>
+    <t>D_SBP028_17S_PR</t>
+  </si>
+  <si>
+    <t>D_JBC002_17N_PR</t>
+  </si>
+  <si>
+    <t>D_CRK005_17N_NR</t>
+  </si>
+  <si>
+    <t>D_SAC294_03_PA</t>
+  </si>
+  <si>
+    <t>D_CAA143_90_PA2</t>
+  </si>
+  <si>
+    <t>D_WTPCSD_02_PA</t>
+  </si>
+  <si>
+    <t>D_DMC034_71_PA2</t>
+  </si>
+  <si>
+    <t>D_XCC025_72_PA</t>
+  </si>
+  <si>
+    <t>D_WTPBLV_03_PU2</t>
+  </si>
+  <si>
+    <t>D_WTPCSD_02_PU</t>
+  </si>
+  <si>
+    <t>D_WKYTN_02_PU</t>
+  </si>
+  <si>
+    <t>D_WTPJMS_03_PU1</t>
+  </si>
+  <si>
+    <t>D_FOLSM_WTPSJP_CVP</t>
+  </si>
+  <si>
+    <t>DIVERSION-CVP</t>
+  </si>
+  <si>
+    <t>D_NFA016_WTPWAL_CVP</t>
+  </si>
+  <si>
+    <t>D_WTPJJO_50_PU</t>
+  </si>
+  <si>
+    <t>D_WTPFTH_02_SU</t>
+  </si>
+  <si>
+    <t>D_WTPFTH_03_SU</t>
+  </si>
+  <si>
+    <t>D_WTPBUK_03_SU</t>
+  </si>
+  <si>
+    <t>D_SAC296_02_SA</t>
+  </si>
+  <si>
+    <t>D_SAC289_03_SA</t>
+  </si>
+  <si>
+    <t>D_GCC027_08N_SA2</t>
+  </si>
+  <si>
+    <t>D_GCC056_08S_SA2</t>
+  </si>
+  <si>
+    <t>D_SAC178_08N_SA1</t>
+  </si>
+  <si>
+    <t>D_SAC159_08N_SA1</t>
+  </si>
+  <si>
+    <t>D_SAC159_08S_SA1</t>
+  </si>
+  <si>
+    <t>D_SAC121_08S_SA3</t>
+  </si>
+  <si>
+    <t>D_SAC109_08S_SA3</t>
+  </si>
+  <si>
+    <t>D_SAC136_18_SA</t>
+  </si>
+  <si>
+    <t>D_SAC122_19_SA</t>
+  </si>
+  <si>
+    <t>D_SAC115_19_SA</t>
+  </si>
+  <si>
+    <t>D_SAC099_19_SA</t>
+  </si>
+  <si>
+    <t>D_SAC091_19_SA</t>
+  </si>
+  <si>
+    <t>D_MTC000_09_SA1</t>
+  </si>
+  <si>
+    <t>D_SAC082_22_SA1</t>
+  </si>
+  <si>
+    <t>D_SAC078_22_SA1</t>
+  </si>
+  <si>
+    <t>D_SAC083_21_SA</t>
+  </si>
+  <si>
+    <t>D_SAC074_21_SA</t>
+  </si>
+  <si>
+    <t>D_MDOTA_73_XA</t>
+  </si>
+  <si>
+    <t>D_DMC111_73_XA</t>
+  </si>
+  <si>
+    <t>D_MDOTA_64_XA</t>
+  </si>
+  <si>
+    <t>D_XCC010_72_XA2</t>
+  </si>
+  <si>
+    <t>D_ARY010_72_XA1</t>
+  </si>
+  <si>
+    <t>D_XCC054_72_XA3</t>
+  </si>
+  <si>
+    <t>D_GCC027_08N_PR1</t>
+  </si>
+  <si>
+    <t>D_MTC000_09_PR</t>
+  </si>
+  <si>
+    <t>D_GCC056_08S_PR</t>
+  </si>
+  <si>
+    <t>D_CBD037_08S_PR</t>
+  </si>
+  <si>
+    <t>D_GCC039_08N_PR2</t>
+  </si>
+  <si>
+    <t>D_MDOTA_91_PR</t>
+  </si>
+  <si>
+    <t>D_ARY010_72_PR6</t>
+  </si>
+  <si>
+    <t>D_XCC025_72_PR6</t>
+  </si>
+  <si>
+    <t>D_XCC054_72_PR5</t>
+  </si>
+  <si>
+    <t>D_VLW008_72_PR5</t>
+  </si>
+  <si>
+    <t>D_ARY010_72_PR3</t>
+  </si>
+  <si>
+    <t>D_XCC033_72_PR4</t>
+  </si>
+  <si>
+    <t>D_XCC033_72_PR2</t>
+  </si>
+  <si>
+    <t>D_VLW008_72_PR1</t>
+  </si>
+  <si>
+    <t>D_CAA046_71_PA7_PAG</t>
+  </si>
+  <si>
+    <t>D_THRMF_11_NU1_PMI</t>
+  </si>
+  <si>
+    <t>D_WTPCYC_16_PU</t>
+  </si>
+  <si>
+    <t>D_CSB038_OBISPO_PCO</t>
+  </si>
+  <si>
+    <t>D_CSB103_BRBRA_PMI</t>
+  </si>
+  <si>
+    <t>D_CSB103_BRBRA_PCO</t>
+  </si>
+  <si>
+    <t>D_CSB103_BRBRA_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB324_AVEK_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB324_AVEK_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB433_MWDSC_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB433_MWDSC_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB433_MWDSC_PIN</t>
+  </si>
+  <si>
+    <t>D_THRMA_WEC000</t>
+  </si>
+  <si>
+    <t>D_THRMA_RVC000</t>
+  </si>
+  <si>
+    <t>D_FTR039_SEC009</t>
+  </si>
+  <si>
+    <t>D_THRMA_JBC000</t>
+  </si>
+  <si>
+    <t>D_FTR021_16_SA</t>
+  </si>
+  <si>
+    <t>D_FTR014_16_SA</t>
+  </si>
+  <si>
+    <t>D_FTR018_15S_SA</t>
+  </si>
+  <si>
+    <t>D_FTR018_16_SA</t>
+  </si>
+  <si>
+    <t>D_WTPMNR_13_NU1</t>
+  </si>
+  <si>
+    <t>D_OROVL_13_NU1</t>
+  </si>
+  <si>
+    <t>D_FPT013_WTPVNY_CVP</t>
+  </si>
+  <si>
+    <t>D_WTPSAC_26S_PU4_CVP</t>
+  </si>
+  <si>
+    <t>D_FPT013_FSC013_EBMUD</t>
+  </si>
+  <si>
+    <t>D_FPT013_FSC013_CCWD</t>
+  </si>
+  <si>
+    <t>D_CCL005_04_PA1</t>
+  </si>
+  <si>
+    <t>D_TCC022_04_PA2</t>
+  </si>
+  <si>
+    <t>D_TCC036_07N_PA</t>
+  </si>
+  <si>
+    <t>D_TCC081_07S_PA</t>
+  </si>
+  <si>
+    <t>D_CBD028_08S_PA</t>
+  </si>
+  <si>
+    <t>D_CBD049_08N_PA</t>
+  </si>
+  <si>
+    <t>D_KLR005_21_PA</t>
+  </si>
+  <si>
+    <t>DG_08N_PR2</t>
+  </si>
+  <si>
+    <t>SW-DELIVERY-GROSS</t>
+  </si>
+  <si>
+    <t>DG_12_NU1</t>
+  </si>
+  <si>
+    <t>DG_11_NU1</t>
+  </si>
+  <si>
+    <t>DG_16_PU</t>
+  </si>
+  <si>
+    <t>D_FTR021_16_PA</t>
+  </si>
+  <si>
+    <t>DG_16_SA</t>
+  </si>
+  <si>
+    <t>DG_15S_SA</t>
+  </si>
+  <si>
+    <t>D_SVRWD_CSTLN_PCO</t>
+  </si>
+  <si>
+    <t>D_SVRWD_CSTLN_PMI</t>
+  </si>
+  <si>
+    <t>D_PRRIS_MWDSC</t>
+  </si>
+  <si>
+    <t>D_PRRIS_MWDSC_PCO</t>
+  </si>
+  <si>
+    <t>D_PRRIS_MWDSC_PIN</t>
+  </si>
+  <si>
+    <t>D_PRRIS_MWDSC_PMI</t>
+  </si>
+  <si>
+    <t>D_PYRMD_VNTRA_LCP</t>
+  </si>
+  <si>
+    <t>D_PYRMD_VNTRA_PCO</t>
+  </si>
+  <si>
+    <t>D_PYRMD_VNTRA_PMI</t>
+  </si>
+  <si>
+    <t>D_CSTIC_VNTRA</t>
+  </si>
+  <si>
+    <t>D_CSTIC_VNTRA_PCO</t>
+  </si>
+  <si>
+    <t>D_CSTIC_VNTRA_PIN</t>
+  </si>
+  <si>
+    <t>D_CSTIC_VNTRA_PMI</t>
+  </si>
+  <si>
+    <t>D_BKR004_NBA009_NAPA_PMI</t>
+  </si>
+  <si>
+    <t>D_BKR004_NBA009_NAPA_PCO</t>
+  </si>
+  <si>
+    <t>D_BKR004_NBA009_NAPA_PIN</t>
+  </si>
+  <si>
+    <t>D_BKR004_NBA009_SCWA_PMI</t>
+  </si>
+  <si>
+    <t>D_BKR004_NBA009_SCWA_PCO</t>
+  </si>
+  <si>
+    <t>D_BKR004_NBA009_SCWA_PIN</t>
+  </si>
+  <si>
+    <t>D_CCC019_CCWD</t>
+  </si>
+  <si>
+    <t>DG_13_NU1</t>
+  </si>
+  <si>
+    <t>D_MDOTA_90_PA1</t>
+  </si>
+  <si>
+    <t>D_CAA109_90_PA1</t>
+  </si>
+  <si>
+    <t>D_CAA143_90_PA1</t>
+  </si>
+  <si>
+    <t>D_CAA155_90_PA1</t>
+  </si>
+  <si>
+    <t>D_CAA172_90_PA1</t>
+  </si>
+  <si>
+    <t>D_MDOTA_91_PA</t>
+  </si>
+  <si>
+    <t>DG_73_XA</t>
+  </si>
+  <si>
+    <t>DG_64_XA</t>
+  </si>
+  <si>
+    <t>DG_72_XA2</t>
+  </si>
+  <si>
+    <t>DG_72_XA1</t>
+  </si>
+  <si>
+    <t>DG_91_PR</t>
+  </si>
+  <si>
+    <t>DG_72_PR6</t>
+  </si>
+  <si>
+    <t>DG_72_PR5</t>
+  </si>
+  <si>
+    <t>DG_72_PR3</t>
+  </si>
+  <si>
+    <t>DG_63_PR3</t>
+  </si>
+  <si>
+    <t>DG_72_PR4</t>
+  </si>
+  <si>
+    <t>D_DMC011_71_PA8</t>
+  </si>
+  <si>
+    <t>D_DMC030_71_PA1</t>
+  </si>
+  <si>
+    <t>D_DMC034_71_PA3</t>
+  </si>
+  <si>
+    <t>D_DMC044_71_PA4</t>
+  </si>
+  <si>
+    <t>D_DMC044_71_PA5</t>
+  </si>
+  <si>
+    <t>D_DMC064_71_PA6</t>
+  </si>
+  <si>
+    <t>D_DMC021_50_PA1</t>
+  </si>
+  <si>
+    <t>D_DMC070_73_PA1</t>
+  </si>
+  <si>
+    <t>D_CAA087_73_PA1</t>
+  </si>
+  <si>
+    <t>D_DMC105_73_PA2</t>
+  </si>
+  <si>
+    <t>D_CAA109_73_PA3</t>
+  </si>
+  <si>
+    <t>D_DMC091_73_PA3</t>
+  </si>
+  <si>
+    <t>DG_72_XA3</t>
+  </si>
+  <si>
+    <t>DG_72_PR2</t>
+  </si>
+  <si>
+    <t>DG_72_PR1</t>
+  </si>
+  <si>
+    <t>D_PCH000_SBCWD_PA</t>
+  </si>
+  <si>
+    <t>D_PCH000_SCVWD_PA</t>
+  </si>
+  <si>
+    <t>D_PCH000_SBCWD_PU</t>
+  </si>
+  <si>
+    <t>D_PCH000_SCVWD_PU</t>
+  </si>
+  <si>
+    <t>DG_11_SA1</t>
+  </si>
+  <si>
+    <t>DG_11_SA3</t>
+  </si>
+  <si>
+    <t>D_FOLSM_WTPEDH_CVP</t>
+  </si>
+  <si>
+    <t>D_FOLSM_EDCOCA_CVP</t>
+  </si>
+  <si>
+    <t>D_FOLSM_PCWA_CVP</t>
+  </si>
+  <si>
+    <t>D_FOLSM_WTPFOL_CVP</t>
+  </si>
+  <si>
+    <t>D_FOLSM_WTPRSV_CVP</t>
+  </si>
+  <si>
+    <t>D_CAA046_71_PA7_PIN</t>
+  </si>
+  <si>
+    <t>D_CAA046_71_PA7_PCO</t>
+  </si>
+  <si>
+    <t>D_SBA009_ACFC_PMI</t>
+  </si>
+  <si>
+    <t>D_SBA009_ACFC_PCO</t>
+  </si>
+  <si>
+    <t>D_SBA009_ACFC_PIN</t>
+  </si>
+  <si>
+    <t>D_SBA020_ACFC_PMI</t>
+  </si>
+  <si>
+    <t>D_SBA020_ACFC_PCO</t>
+  </si>
+  <si>
+    <t>D_SBA029_ACWD_PMI</t>
+  </si>
+  <si>
+    <t>D_SBA029_ACWD_PCO</t>
+  </si>
+  <si>
+    <t>D_SBA029_ACWD_PIN</t>
+  </si>
+  <si>
+    <t>D_SBA036_SCVWD_PMI</t>
+  </si>
+  <si>
+    <t>D_SBA036_SCVWD_PCO</t>
+  </si>
+  <si>
+    <t>D_SBA036_SCVWD_PIN</t>
+  </si>
+  <si>
+    <t>D_CAA143_90_PU</t>
+  </si>
+  <si>
+    <t>D_CAA156_90_PU</t>
+  </si>
+  <si>
+    <t>D_CAA165_90_PU</t>
+  </si>
+  <si>
+    <t>D_CAA173_EMPIRE_PAG</t>
+  </si>
+  <si>
+    <t>D_CAA173_EMPIRE_PCO</t>
+  </si>
+  <si>
+    <t>D_CAA173_EMPIRE_PIN</t>
+  </si>
+  <si>
+    <t>D_CAA181_KINGS_PAG</t>
+  </si>
+  <si>
+    <t>D_CAA181_KINGS_PCO</t>
+  </si>
+  <si>
+    <t>D_CAA181_KINGS_PIN</t>
+  </si>
+  <si>
+    <t>D_CAA183_TULARE_PAG</t>
+  </si>
+  <si>
+    <t>D_CAA183_TULARE_PCO</t>
+  </si>
+  <si>
+    <t>D_CAA183_TULARE_PIN</t>
+  </si>
+  <si>
+    <t>D_CAA184_DUDLEY_PAG</t>
+  </si>
+  <si>
+    <t>D_CAA184_DUDLEY_PCO</t>
+  </si>
+  <si>
+    <t>D_CAA184_DUDLEY_PIN</t>
+  </si>
+  <si>
+    <t>D_CAA194_KERN_PAG</t>
+  </si>
+  <si>
+    <t>D_CAA194_KERN_PCO</t>
+  </si>
+  <si>
+    <t>D_CAA194_KERNA_PMI</t>
+  </si>
+  <si>
+    <t>D_CAA194_KERNB_PMI</t>
+  </si>
+  <si>
+    <t>D_CAA238_CVPCV</t>
+  </si>
+  <si>
+    <t>D_CAA239_CVPRF</t>
+  </si>
+  <si>
+    <t>D_CAA242_KERN_PAG</t>
+  </si>
+  <si>
+    <t>D_CAA242_KERN_PCO</t>
+  </si>
+  <si>
+    <t>D_CAA242_KERN_PIN</t>
+  </si>
+  <si>
+    <t>D_CAA279_KERN</t>
+  </si>
+  <si>
+    <t>D_CSB015_KERN_BMWD_PAG</t>
+  </si>
+  <si>
+    <t>D_CSB015_KERN_BMWD_PCO</t>
+  </si>
+  <si>
+    <t>D_CSB009_CLRTA1_DDWD_PAG</t>
+  </si>
+  <si>
+    <t>D_CSB009_CLRTA1_DDWD_PCO</t>
+  </si>
+  <si>
+    <t>D_CSB009_CLRTA1_DDWD_PIN</t>
+  </si>
+  <si>
+    <t>D_CSB038_OBISPO_PIN</t>
+  </si>
+  <si>
+    <t>D_CSB038_OBISPO_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB324_AVEK_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB347_PLMDL_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB347_PLMDL_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB347_PLMDL_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB355_LROCK_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB355_LROCK_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB403_MOJVE_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB403_MOJVE_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB407_CCHLA_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB407_CCHLA_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB407_CCHLA_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB408_DESRT_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB408_DESRT_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB408_DESRT_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB413_MWDSC_LCP</t>
+  </si>
+  <si>
+    <t>D_ESB413_MWDSC_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB413_MWDSC_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB413_MWDSC_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB414_BRDNO_LCP</t>
+  </si>
+  <si>
+    <t>D_ESB414_BRDNO_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB414_BRDNO_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB414_BRDNO_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB415_GABRL_LCP</t>
+  </si>
+  <si>
+    <t>D_ESB415_GABRL_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB415_GABRL_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB415_GABRL_PMI</t>
+  </si>
+  <si>
+    <t>D_ESB420_GRGNO_LCP</t>
+  </si>
+  <si>
+    <t>D_ESB420_GRGNO_PCO</t>
+  </si>
+  <si>
+    <t>D_ESB420_GRGNO_PIN</t>
+  </si>
+  <si>
+    <t>D_ESB420_GRGNO_PMI</t>
+  </si>
+  <si>
+    <t>D_WSB031_MWDSC_LCP</t>
+  </si>
+  <si>
+    <t>D_WSB031_MWDSC_PCO</t>
+  </si>
+  <si>
+    <t>D_WSB031_MWDSC_PIN</t>
+  </si>
+  <si>
+    <t>D_WSB031_MWDSC_PMI</t>
+  </si>
+  <si>
+    <t>D_WSB032_CLRTA2_LCP</t>
+  </si>
+  <si>
+    <t>D_WSB032_CLRTA2_PCO</t>
+  </si>
+  <si>
+    <t>D_WSB032_CLRTA2_PMI</t>
+  </si>
+  <si>
+    <t>D_FSC015_60N_NA2</t>
+  </si>
+  <si>
+    <t>D_FSC025_60N_PU_CVP</t>
+  </si>
+  <si>
+    <t>PERDV_CVPAG_S</t>
+  </si>
+  <si>
+    <t>PERCENT-DELIVERY</t>
+  </si>
+  <si>
+    <t>PERDV_CVPAG_SYS</t>
+  </si>
+  <si>
+    <t>PERDV_CVPEX_S</t>
+  </si>
+  <si>
+    <t>PERDV_CVPMI_S</t>
+  </si>
+  <si>
+    <t>PERDV_CVPMI_SYS</t>
+  </si>
+  <si>
+    <t>PERDV_CVPRF_SYS</t>
+  </si>
+  <si>
+    <t>PERDV_CVPSC_SYS</t>
+  </si>
+  <si>
+    <t>PERDV_SWP_AG1</t>
+  </si>
+  <si>
+    <t>PERDV_SWP_FSC</t>
+  </si>
+  <si>
+    <t>PERDV_SWP_MWD1</t>
+  </si>
+  <si>
+    <t>SWP_CO_TOTAL</t>
+  </si>
+  <si>
+    <t>SWP_DELIVERY</t>
+  </si>
+  <si>
+    <t>SWP_IN_TOTAL</t>
+  </si>
+  <si>
+    <t>SWP_TA_FEATH</t>
+  </si>
+  <si>
+    <t>SWP_TA_NBAY</t>
+  </si>
+  <si>
+    <t>SWP_TA_TOTAL</t>
+  </si>
+  <si>
+    <t>D_MLRTN_FRK_C1</t>
+  </si>
+  <si>
+    <t>D_MLRTN_FRK_C2</t>
+  </si>
+  <si>
+    <t>D_MLRTN_MDC_C1</t>
+  </si>
+  <si>
+    <t>D_MLRTN_MDC_C2</t>
+  </si>
+  <si>
+    <t>D_TCC111_07S_PA</t>
+  </si>
+  <si>
+    <t>D_ARY010_72_PR4</t>
+  </si>
+  <si>
+    <t>D_SAC162_09_SA2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,8 +1778,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1003,6 +1826,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1047,11 +1882,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1144,12 +1980,42 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{04BB39D2-74C8-436F-88D7-947A701CDBD7}"/>
+    <cellStyle name="Normal 9" xfId="2" xr:uid="{C0E7D01C-6074-486B-826F-55584AB9AB24}"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1179,6 +2045,16 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -1466,6 +2342,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1766,22 +2646,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E97D62-E007-4D94-B471-28936CBA853B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P345"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="3" max="3" width="60.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" customWidth="1"/>
-    <col min="7" max="7" width="32.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" customWidth="1"/>
-    <col min="9" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="32.28515625" customWidth="1"/>
-    <col min="13" max="13" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.41796875" customWidth="1"/>
+    <col min="3" max="3" width="60.41796875" customWidth="1"/>
+    <col min="4" max="4" width="22.41796875" customWidth="1"/>
+    <col min="5" max="5" width="16.83984375" customWidth="1"/>
+    <col min="6" max="6" width="21.578125" customWidth="1"/>
+    <col min="7" max="7" width="32.15625" customWidth="1"/>
+    <col min="8" max="8" width="16.26171875" customWidth="1"/>
+    <col min="9" max="10" width="20.68359375" customWidth="1"/>
+    <col min="11" max="11" width="32.26171875" customWidth="1"/>
+    <col min="13" max="13" width="22.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1831,7 +2711,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="11" t="s">
         <v>74</v>
       </c>
@@ -1878,7 +2758,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11" t="s">
         <v>46</v>
       </c>
@@ -1925,7 +2805,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="18" t="s">
         <v>98</v>
       </c>
@@ -1973,7 +2853,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="11" t="s">
         <v>46</v>
       </c>
@@ -2020,7 +2900,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="18" t="s">
         <v>104</v>
       </c>
@@ -2068,7 +2948,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11" t="s">
         <v>46</v>
       </c>
@@ -2115,7 +2995,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="11" t="s">
         <v>46</v>
       </c>
@@ -2162,7 +3042,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="11" t="s">
         <v>46</v>
       </c>
@@ -2209,7 +3089,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="18" t="s">
         <v>94</v>
       </c>
@@ -2257,7 +3137,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="18" t="s">
         <v>108</v>
       </c>
@@ -2305,7 +3185,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="11" t="s">
         <v>74</v>
       </c>
@@ -2352,7 +3232,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="11" t="s">
         <v>74</v>
       </c>
@@ -2399,7 +3279,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="18" t="s">
         <v>131</v>
       </c>
@@ -2447,7 +3327,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="18" t="s">
         <v>135</v>
       </c>
@@ -2495,7 +3375,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="18" t="s">
         <v>189</v>
       </c>
@@ -2543,7 +3423,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="18" t="s">
         <v>145</v>
       </c>
@@ -2591,7 +3471,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="18" t="s">
         <v>185</v>
       </c>
@@ -2639,7 +3519,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="18" t="s">
         <v>257</v>
       </c>
@@ -2687,7 +3567,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
         <v>243</v>
       </c>
@@ -2735,7 +3615,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="5" t="s">
         <v>229</v>
       </c>
@@ -2783,7 +3663,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5" t="s">
         <v>282</v>
       </c>
@@ -2831,7 +3711,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5" t="s">
         <v>275</v>
       </c>
@@ -2879,7 +3759,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5" t="s">
         <v>32</v>
       </c>
@@ -2927,7 +3807,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
         <v>268</v>
       </c>
@@ -2975,7 +3855,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5" t="s">
         <v>223</v>
       </c>
@@ -3023,7 +3903,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="8" t="s">
         <v>249</v>
       </c>
@@ -3071,7 +3951,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="8" t="s">
         <v>245</v>
       </c>
@@ -3119,7 +3999,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11" t="s">
         <v>46</v>
       </c>
@@ -3166,7 +4046,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8" t="s">
         <v>260</v>
       </c>
@@ -3214,7 +4094,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="11" t="s">
         <v>46</v>
       </c>
@@ -3261,7 +4141,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="18" t="s">
         <v>87</v>
       </c>
@@ -3309,7 +4189,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="18" t="s">
         <v>285</v>
       </c>
@@ -3357,7 +4237,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="8" t="s">
         <v>235</v>
       </c>
@@ -3405,7 +4285,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="8" t="s">
         <v>231</v>
       </c>
@@ -3453,7 +4333,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="11" t="s">
         <v>46</v>
       </c>
@@ -3501,7 +4381,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="11" t="s">
         <v>46</v>
       </c>
@@ -3548,7 +4428,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="11" t="s">
         <v>46</v>
       </c>
@@ -3596,7 +4476,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="11" t="s">
         <v>74</v>
       </c>
@@ -3643,7 +4523,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="8" t="s">
         <v>69</v>
       </c>
@@ -3693,7 +4573,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="11" t="s">
         <v>74</v>
       </c>
@@ -3741,7 +4621,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="8" t="s">
         <v>201</v>
       </c>
@@ -3789,7 +4669,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="11" t="s">
         <v>46</v>
       </c>
@@ -3837,7 +4717,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="8" t="s">
         <v>213</v>
       </c>
@@ -3885,7 +4765,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="29" t="s">
         <v>205</v>
       </c>
@@ -3933,7 +4813,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="8" t="s">
         <v>38</v>
       </c>
@@ -3981,7 +4861,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="29" t="s">
         <v>209</v>
       </c>
@@ -4029,7 +4909,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="8" t="s">
         <v>54</v>
       </c>
@@ -4077,7 +4957,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="8" t="s">
         <v>197</v>
       </c>
@@ -4125,7 +5005,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="11" t="s">
         <v>46</v>
       </c>
@@ -4173,7 +5053,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="8" t="s">
         <v>58</v>
       </c>
@@ -4221,7 +5101,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="8" t="s">
         <v>62</v>
       </c>
@@ -4269,7 +5149,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="8" t="s">
         <v>165</v>
       </c>
@@ -4317,7 +5197,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="8" t="s">
         <v>173</v>
       </c>
@@ -4365,7 +5245,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="8" t="s">
         <v>169</v>
       </c>
@@ -4413,7 +5293,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="8" t="s">
         <v>177</v>
       </c>
@@ -4461,7 +5341,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="8" t="s">
         <v>181</v>
       </c>
@@ -4509,7 +5389,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="11" t="s">
         <v>46</v>
       </c>
@@ -4557,7 +5437,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="8" t="s">
         <v>253</v>
       </c>
@@ -4605,7 +5485,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="8" t="s">
         <v>50</v>
       </c>
@@ -4653,7 +5533,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="8" t="s">
         <v>77</v>
       </c>
@@ -4701,7 +5581,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="8" t="s">
         <v>217</v>
       </c>
@@ -4749,7 +5629,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="5" t="s">
         <v>239</v>
       </c>
@@ -4797,7 +5677,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5" t="s">
         <v>225</v>
       </c>
@@ -4845,7 +5725,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5" t="s">
         <v>278</v>
       </c>
@@ -4893,7 +5773,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5" t="s">
         <v>271</v>
       </c>
@@ -4941,7 +5821,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="23" t="s">
         <v>120</v>
       </c>
@@ -4989,7 +5869,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5" t="s">
         <v>28</v>
       </c>
@@ -5037,7 +5917,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5" t="s">
         <v>16</v>
       </c>
@@ -5085,7 +5965,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5" t="s">
         <v>264</v>
       </c>
@@ -5133,7 +6013,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="17" t="s">
         <v>193</v>
       </c>
@@ -5181,7 +6061,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="11" t="s">
         <v>46</v>
       </c>
@@ -5227,107 +6107,4755 @@
       </c>
       <c r="P72" s="12">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C73" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="E73" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I73" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="J73" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C74" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="E74" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I74" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="J74" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C75" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I75" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="J75" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C76" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="E76" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I76" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="J76" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C77" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="E77" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I77" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="J77" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C78" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="E78" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I78" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="J78" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C79" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="E79" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I79" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="J79" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="C80" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="E80" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I80" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="J80" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C81" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="E81" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I81" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="J81" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C82" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="E82" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I82" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="J82" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C83" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="E83" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I83" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J83" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C84" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="E84" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I84" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="J84" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C85" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="E85" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I85" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="J85" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C86" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="E86" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I86" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="J86" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C87" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="E87" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I87" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="J87" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C88" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="E88" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I88" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="J88" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C89" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="E89" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I89" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="J89" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C90" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="E90" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I90" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="J90" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C91" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="E91" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I91" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="J91" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C92" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="E92" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I92" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="J92" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C93" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="E93" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I93" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="J93" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C94" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E94" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I94" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="J94" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C95" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="E95" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I95" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="J95" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K95" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C96" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="E96" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I96" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="J96" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C97" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="E97" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I97" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="J97" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C98" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="E98" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I98" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="J98" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K98" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C99" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="E99" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="J99" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K99" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C100" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="E100" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I100" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="J100" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K100" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C101" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E101" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I101" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="J101" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K101" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C102" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="E102" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I102" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="J102" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K102" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C103" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="E103" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I103" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="J103" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K103" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C104" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="E104" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I104" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="J104" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K104" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C105" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="E105" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I105" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="J105" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K105" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C106" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="E106" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I106" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="J106" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K106" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C107" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="E107" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I107" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="J107" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K107" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C108" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="E108" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I108" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="J108" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K108" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C109" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="E109" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I109" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="J109" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K109" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C110" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="E110" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I110" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="J110" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K110" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C111" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="E111" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I111" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="J111" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K111" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C112" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="E112" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I112" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="J112" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K112" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C113" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="E113" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I113" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="J113" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K113" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C114" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="E114" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I114" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="J114" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K114" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C115" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="E115" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I115" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="J115" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K115" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C116" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="E116" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I116" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="J116" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K116" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C117" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="E117" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I117" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="J117" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K117" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C118" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="E118" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I118" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="J118" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K118" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C119" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="E119" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I119" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="J119" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K119" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C120" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="E120" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I120" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="J120" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K120" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C121" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="E121" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I121" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="J121" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K121" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C122" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E122" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I122" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="J122" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K122" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C123" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E123" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I123" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="J123" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K123" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C124" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="E124" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I124" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="J124" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K124" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C125" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="E125" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I125" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="J125" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K125" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C126" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="E126" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I126" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="J126" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K126" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C127" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="E127" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I127" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="J127" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K127" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C128" s="34" t="s">
+        <v>559</v>
+      </c>
+      <c r="E128" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I128" s="34" t="s">
+        <v>559</v>
+      </c>
+      <c r="J128" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K128" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C129" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="E129" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I129" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="J129" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K129" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="130" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C130" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="E130" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I130" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="J130" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K130" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C131" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="E131" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I131" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="J131" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K131" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C132" s="34" t="s">
+        <v>350</v>
+      </c>
+      <c r="E132" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I132" s="34" t="s">
+        <v>350</v>
+      </c>
+      <c r="J132" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K132" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C133" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="E133" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I133" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="J133" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K133" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C134" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="E134" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I134" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="J134" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K134" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C135" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="E135" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I135" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="J135" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K135" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C136" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="E136" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I136" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="J136" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K136" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="137" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C137" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="E137" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I137" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="J137" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K137" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C138" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="E138" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I138" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="J138" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K138" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="139" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C139" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="E139" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I139" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="J139" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K139" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C140" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="E140" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I140" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="J140" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K140" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C141" s="34" t="s">
+        <v>359</v>
+      </c>
+      <c r="E141" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I141" s="34" t="s">
+        <v>359</v>
+      </c>
+      <c r="J141" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K141" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C142" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="E142" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I142" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="J142" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K142" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="143" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C143" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="E143" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I143" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="J143" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K143" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C144" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="E144" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I144" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="J144" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K144" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C145" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="E145" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I145" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="J145" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K145" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C146" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="E146" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I146" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="J146" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K146" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C147" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="E147" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I147" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="J147" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K147" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C148" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="E148" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I148" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="J148" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K148" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C149" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="E149" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I149" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="J149" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K149" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C150" s="34" t="s">
+        <v>368</v>
+      </c>
+      <c r="E150" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I150" s="34" t="s">
+        <v>368</v>
+      </c>
+      <c r="J150" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K150" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="151" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C151" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="E151" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I151" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="J151" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K151" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C152" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="E152" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I152" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="J152" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K152" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="153" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C153" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="E153" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I153" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="J153" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K153" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="154" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C154" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="E154" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I154" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="J154" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K154" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C155" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="E155" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I155" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="J155" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K155" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C156" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="E156" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I156" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="J156" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K156" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C157" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="E157" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I157" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="J157" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K157" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="158" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C158" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="E158" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I158" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="J158" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K158" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C159" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="E159" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I159" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="J159" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K159" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C160" s="36" t="s">
+        <v>378</v>
+      </c>
+      <c r="E160" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I160" s="36" t="s">
+        <v>378</v>
+      </c>
+      <c r="J160" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K160" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C161" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="E161" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I161" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="J161" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K161" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C162" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="E162" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I162" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="J162" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K162" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C163" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="E163" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I163" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="J163" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K163" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C164" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="E164" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I164" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="J164" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K164" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C165" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="E165" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I165" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="J165" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K165" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C166" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="E166" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I166" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="J166" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K166" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C167" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="E167" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I167" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="J167" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K167" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C168" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="E168" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I168" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="J168" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K168" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C169" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="E169" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I169" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="J169" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K169" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C170" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="E170" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I170" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="J170" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K170" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C171" s="34" t="s">
+        <v>390</v>
+      </c>
+      <c r="E171" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I171" s="34" t="s">
+        <v>390</v>
+      </c>
+      <c r="J171" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K171" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C172" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="E172" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I172" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="J172" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K172" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C173" s="34" t="s">
+        <v>392</v>
+      </c>
+      <c r="E173" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I173" s="34" t="s">
+        <v>392</v>
+      </c>
+      <c r="J173" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K173" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C174" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="E174" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I174" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="J174" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K174" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C175" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="E175" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I175" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="J175" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K175" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C176" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="E176" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I176" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="J176" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K176" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C177" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="E177" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I177" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="J177" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K177" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C178" s="34" t="s">
+        <v>397</v>
+      </c>
+      <c r="E178" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I178" s="34" t="s">
+        <v>397</v>
+      </c>
+      <c r="J178" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K178" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="179" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C179" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="E179" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I179" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="J179" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K179" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C180" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="E180" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I180" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="J180" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K180" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C181" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="E181" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I181" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="J181" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K181" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C182" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="E182" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I182" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="J182" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K182" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="183" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C183" s="34" t="s">
+        <v>402</v>
+      </c>
+      <c r="E183" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I183" s="34" t="s">
+        <v>402</v>
+      </c>
+      <c r="J183" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K183" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C184" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="E184" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I184" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="J184" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K184" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="185" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C185" s="34" t="s">
+        <v>404</v>
+      </c>
+      <c r="E185" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I185" s="34" t="s">
+        <v>404</v>
+      </c>
+      <c r="J185" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K185" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C186" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="E186" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I186" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="J186" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K186" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C187" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="E187" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I187" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="J187" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K187" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="188" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C188" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="E188" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I188" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="J188" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K188" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C189" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="E189" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I189" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="J189" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K189" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C190" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="E190" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I190" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="J190" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K190" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C191" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="E191" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I191" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="J191" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K191" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C192" s="37" t="s">
+        <v>411</v>
+      </c>
+      <c r="E192" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I192" s="37" t="s">
+        <v>411</v>
+      </c>
+      <c r="J192" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K192" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C193" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="E193" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I193" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="J193" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K193" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C194" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="E194" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I194" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="J194" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K194" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C195" s="37" t="s">
+        <v>414</v>
+      </c>
+      <c r="E195" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I195" s="37" t="s">
+        <v>414</v>
+      </c>
+      <c r="J195" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K195" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C196" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="E196" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I196" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="J196" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K196" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C197" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="E197" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I197" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="J197" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K197" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C198" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="E198" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I198" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="J198" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K198" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C199" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="E199" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I199" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="J199" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K199" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C200" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="E200" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I200" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="J200" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K200" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C201" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="E201" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I201" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="J201" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K201" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C202" s="34" t="s">
+        <v>421</v>
+      </c>
+      <c r="E202" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I202" s="34" t="s">
+        <v>421</v>
+      </c>
+      <c r="J202" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K202" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C203" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="E203" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I203" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="J203" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K203" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C204" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="E204" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I204" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="J204" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K204" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C205" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="E205" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I205" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="J205" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K205" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C206" s="34" t="s">
+        <v>425</v>
+      </c>
+      <c r="E206" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I206" s="34" t="s">
+        <v>425</v>
+      </c>
+      <c r="J206" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K206" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C207" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="E207" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I207" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="J207" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K207" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C208" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="E208" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I208" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="J208" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K208" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C209" s="36" t="s">
+        <v>428</v>
+      </c>
+      <c r="E209" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I209" s="36" t="s">
+        <v>428</v>
+      </c>
+      <c r="J209" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K209" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C210" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="E210" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I210" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="J210" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K210" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="211" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C211" s="36" t="s">
+        <v>430</v>
+      </c>
+      <c r="E211" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I211" s="36" t="s">
+        <v>430</v>
+      </c>
+      <c r="J211" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K211" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="212" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C212" s="36" t="s">
+        <v>431</v>
+      </c>
+      <c r="E212" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I212" s="36" t="s">
+        <v>431</v>
+      </c>
+      <c r="J212" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K212" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C213" s="36" t="s">
+        <v>432</v>
+      </c>
+      <c r="E213" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I213" s="36" t="s">
+        <v>432</v>
+      </c>
+      <c r="J213" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K213" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="214" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C214" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="E214" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I214" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="J214" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K214" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C215" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="E215" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I215" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="J215" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K215" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C216" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="E216" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I216" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="J216" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K216" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C217" s="36" t="s">
+        <v>436</v>
+      </c>
+      <c r="E217" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I217" s="36" t="s">
+        <v>436</v>
+      </c>
+      <c r="J217" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K217" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="218" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C218" s="37" t="s">
+        <v>437</v>
+      </c>
+      <c r="E218" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I218" s="37" t="s">
+        <v>437</v>
+      </c>
+      <c r="J218" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K218" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="219" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C219" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="E219" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I219" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="J219" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K219" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="220" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C220" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="E220" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I220" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="J220" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K220" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C221" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="E221" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I221" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="J221" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K221" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C222" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="E222" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I222" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="J222" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K222" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="223" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C223" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E223" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I223" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="J223" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K223" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="224" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C224" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="E224" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I224" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="J224" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K224" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C225" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="E225" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I225" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="J225" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K225" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C226" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="E226" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I226" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="J226" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K226" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="227" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C227" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="E227" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I227" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="J227" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K227" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="228" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C228" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="E228" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I228" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="J228" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="K228" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C229" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="E229" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I229" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="J229" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K229" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="230" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C230" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="E230" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I230" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="J230" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K230" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="231" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C231" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="E231" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I231" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="J231" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K231" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C232" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="E232" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I232" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="J232" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K232" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="233" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C233" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="E233" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I233" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="J233" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K233" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="234" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C234" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="E234" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I234" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="J234" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K234" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="235" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C235" s="34" t="s">
+        <v>454</v>
+      </c>
+      <c r="E235" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I235" s="34" t="s">
+        <v>454</v>
+      </c>
+      <c r="J235" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K235" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="236" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C236" s="38" t="s">
+        <v>455</v>
+      </c>
+      <c r="E236" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I236" s="38" t="s">
+        <v>455</v>
+      </c>
+      <c r="J236" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K236" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C237" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="E237" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I237" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="J237" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K237" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="238" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C238" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="E238" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I238" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="J238" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K238" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="239" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C239" s="38" t="s">
+        <v>458</v>
+      </c>
+      <c r="E239" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I239" s="38" t="s">
+        <v>458</v>
+      </c>
+      <c r="J239" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K239" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="240" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C240" s="38" t="s">
+        <v>459</v>
+      </c>
+      <c r="E240" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I240" s="38" t="s">
+        <v>459</v>
+      </c>
+      <c r="J240" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K240" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="241" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C241" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="E241" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I241" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="J241" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K241" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C242" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="E242" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I242" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="J242" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K242" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="243" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C243" s="38" t="s">
+        <v>462</v>
+      </c>
+      <c r="E243" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I243" s="38" t="s">
+        <v>462</v>
+      </c>
+      <c r="J243" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K243" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="244" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C244" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="E244" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I244" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="J244" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K244" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="245" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C245" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="E245" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I245" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="J245" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K245" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C246" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="E246" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I246" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="J246" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K246" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C247" s="39" t="s">
+        <v>466</v>
+      </c>
+      <c r="E247" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I247" s="39" t="s">
+        <v>466</v>
+      </c>
+      <c r="J247" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K247" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C248" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="E248" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I248" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="J248" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K248" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="249" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C249" s="39" t="s">
+        <v>468</v>
+      </c>
+      <c r="E249" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I249" s="39" t="s">
+        <v>468</v>
+      </c>
+      <c r="J249" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K249" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="250" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C250" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="E250" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I250" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="J250" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K250" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C251" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="E251" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I251" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="J251" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K251" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C252" s="34" t="s">
+        <v>471</v>
+      </c>
+      <c r="E252" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I252" s="34" t="s">
+        <v>471</v>
+      </c>
+      <c r="J252" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K252" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="253" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C253" s="34" t="s">
+        <v>472</v>
+      </c>
+      <c r="E253" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I253" s="34" t="s">
+        <v>472</v>
+      </c>
+      <c r="J253" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K253" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="254" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C254" s="34" t="s">
+        <v>473</v>
+      </c>
+      <c r="E254" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I254" s="34" t="s">
+        <v>473</v>
+      </c>
+      <c r="J254" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K254" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="255" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C255" s="34" t="s">
+        <v>474</v>
+      </c>
+      <c r="E255" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I255" s="34" t="s">
+        <v>474</v>
+      </c>
+      <c r="J255" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K255" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="256" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C256" s="34" t="s">
+        <v>475</v>
+      </c>
+      <c r="E256" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I256" s="34" t="s">
+        <v>475</v>
+      </c>
+      <c r="J256" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K256" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="257" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C257" s="34" t="s">
+        <v>476</v>
+      </c>
+      <c r="E257" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I257" s="34" t="s">
+        <v>476</v>
+      </c>
+      <c r="J257" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K257" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="258" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C258" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="E258" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I258" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="J258" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K258" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C259" s="34" t="s">
+        <v>478</v>
+      </c>
+      <c r="E259" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I259" s="34" t="s">
+        <v>478</v>
+      </c>
+      <c r="J259" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K259" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="260" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C260" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E260" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I260" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="J260" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K260" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="261" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C261" s="34" t="s">
+        <v>480</v>
+      </c>
+      <c r="E261" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I261" s="34" t="s">
+        <v>480</v>
+      </c>
+      <c r="J261" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K261" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="262" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C262" s="38" t="s">
+        <v>481</v>
+      </c>
+      <c r="E262" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I262" s="38" t="s">
+        <v>481</v>
+      </c>
+      <c r="J262" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K262" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="263" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C263" s="38" t="s">
+        <v>482</v>
+      </c>
+      <c r="E263" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I263" s="38" t="s">
+        <v>482</v>
+      </c>
+      <c r="J263" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K263" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="264" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C264" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="E264" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I264" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="J264" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K264" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="265" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C265" s="38" t="s">
+        <v>484</v>
+      </c>
+      <c r="E265" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I265" s="38" t="s">
+        <v>484</v>
+      </c>
+      <c r="J265" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K265" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="266" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C266" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="E266" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I266" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="J266" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K266" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C267" s="38" t="s">
+        <v>486</v>
+      </c>
+      <c r="E267" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I267" s="38" t="s">
+        <v>486</v>
+      </c>
+      <c r="J267" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K267" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="268" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C268" s="40" t="s">
+        <v>487</v>
+      </c>
+      <c r="E268" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I268" s="40" t="s">
+        <v>487</v>
+      </c>
+      <c r="J268" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K268" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="269" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C269" s="40" t="s">
+        <v>488</v>
+      </c>
+      <c r="E269" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I269" s="40" t="s">
+        <v>488</v>
+      </c>
+      <c r="J269" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K269" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="270" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C270" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E270" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I270" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="J270" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K270" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="271" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C271" s="38" t="s">
+        <v>490</v>
+      </c>
+      <c r="E271" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I271" s="38" t="s">
+        <v>490</v>
+      </c>
+      <c r="J271" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K271" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="272" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C272" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="E272" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I272" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="J272" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K272" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C273" s="40" t="s">
+        <v>492</v>
+      </c>
+      <c r="E273" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I273" s="40" t="s">
+        <v>492</v>
+      </c>
+      <c r="J273" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K273" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="274" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C274" s="34" t="s">
+        <v>493</v>
+      </c>
+      <c r="E274" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I274" s="34" t="s">
+        <v>493</v>
+      </c>
+      <c r="J274" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K274" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="275" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C275" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="E275" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I275" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="J275" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K275" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="276" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C276" s="34" t="s">
+        <v>495</v>
+      </c>
+      <c r="E276" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I276" s="34" t="s">
+        <v>495</v>
+      </c>
+      <c r="J276" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K276" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="277" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C277" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="E277" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I277" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="J277" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K277" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="278" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C278" s="34" t="s">
+        <v>496</v>
+      </c>
+      <c r="E278" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I278" s="34" t="s">
+        <v>496</v>
+      </c>
+      <c r="J278" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K278" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="279" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C279" s="34" t="s">
+        <v>497</v>
+      </c>
+      <c r="E279" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I279" s="34" t="s">
+        <v>497</v>
+      </c>
+      <c r="J279" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K279" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="280" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C280" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="E280" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I280" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="J280" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K280" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="281" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C281" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="E281" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I281" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="J281" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K281" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="282" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C282" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="E282" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I282" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="J282" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K282" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="283" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C283" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="E283" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I283" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="J283" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K283" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="284" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C284" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="E284" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I284" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="J284" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K284" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="285" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C285" s="34" t="s">
+        <v>498</v>
+      </c>
+      <c r="E285" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I285" s="34" t="s">
+        <v>498</v>
+      </c>
+      <c r="J285" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K285" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="286" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C286" s="34" t="s">
+        <v>499</v>
+      </c>
+      <c r="E286" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I286" s="34" t="s">
+        <v>499</v>
+      </c>
+      <c r="J286" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K286" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="287" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C287" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="E287" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I287" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="J287" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K287" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="288" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C288" s="34" t="s">
+        <v>501</v>
+      </c>
+      <c r="E288" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I288" s="34" t="s">
+        <v>501</v>
+      </c>
+      <c r="J288" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K288" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="289" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C289" s="34" t="s">
+        <v>502</v>
+      </c>
+      <c r="E289" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I289" s="34" t="s">
+        <v>502</v>
+      </c>
+      <c r="J289" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K289" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="290" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C290" s="34" t="s">
+        <v>503</v>
+      </c>
+      <c r="E290" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I290" s="34" t="s">
+        <v>503</v>
+      </c>
+      <c r="J290" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K290" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="291" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C291" s="34" t="s">
+        <v>504</v>
+      </c>
+      <c r="E291" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I291" s="34" t="s">
+        <v>504</v>
+      </c>
+      <c r="J291" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K291" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="292" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C292" s="34" t="s">
+        <v>505</v>
+      </c>
+      <c r="E292" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I292" s="34" t="s">
+        <v>505</v>
+      </c>
+      <c r="J292" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K292" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="293" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C293" s="34" t="s">
+        <v>506</v>
+      </c>
+      <c r="E293" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I293" s="34" t="s">
+        <v>506</v>
+      </c>
+      <c r="J293" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K293" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="294" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C294" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="E294" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I294" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="J294" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K294" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="295" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C295" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="E295" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I295" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="J295" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K295" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="296" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C296" s="34" t="s">
+        <v>509</v>
+      </c>
+      <c r="E296" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I296" s="34" t="s">
+        <v>509</v>
+      </c>
+      <c r="J296" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K296" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="297" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C297" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="E297" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I297" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="J297" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K297" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="298" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C298" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="E298" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I298" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="J298" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K298" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="299" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C299" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E299" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I299" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="J299" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K299" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="300" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C300" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="E300" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I300" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="J300" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K300" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="301" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C301" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="E301" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I301" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="J301" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K301" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="302" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C302" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="E302" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I302" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="J302" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K302" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="303" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C303" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="E303" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I303" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="J303" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K303" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="304" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C304" s="34" t="s">
+        <v>517</v>
+      </c>
+      <c r="E304" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I304" s="34" t="s">
+        <v>517</v>
+      </c>
+      <c r="J304" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K304" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="305" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C305" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="E305" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I305" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="J305" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K305" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="306" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C306" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="E306" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I306" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="J306" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K306" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="307" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C307" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="E307" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I307" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="J307" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K307" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="308" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C308" s="34" t="s">
+        <v>521</v>
+      </c>
+      <c r="E308" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I308" s="34" t="s">
+        <v>521</v>
+      </c>
+      <c r="J308" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K308" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="309" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C309" s="34" t="s">
+        <v>522</v>
+      </c>
+      <c r="E309" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I309" s="34" t="s">
+        <v>522</v>
+      </c>
+      <c r="J309" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K309" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="310" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C310" s="34" t="s">
+        <v>523</v>
+      </c>
+      <c r="E310" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I310" s="34" t="s">
+        <v>523</v>
+      </c>
+      <c r="J310" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K310" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="311" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C311" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="E311" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I311" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="J311" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K311" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="312" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C312" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="E312" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I312" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="J312" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K312" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="313" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C313" s="34" t="s">
+        <v>526</v>
+      </c>
+      <c r="E313" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I313" s="34" t="s">
+        <v>526</v>
+      </c>
+      <c r="J313" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K313" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="314" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C314" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="E314" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I314" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="J314" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K314" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="315" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C315" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="E315" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I315" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="J315" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K315" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="316" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C316" s="34" t="s">
+        <v>529</v>
+      </c>
+      <c r="E316" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I316" s="34" t="s">
+        <v>529</v>
+      </c>
+      <c r="J316" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K316" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="317" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C317" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="E317" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I317" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="J317" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K317" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="318" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C318" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="E318" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I318" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="J318" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K318" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="319" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C319" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E319" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I319" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="J319" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K319" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="320" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C320" s="34" t="s">
+        <v>533</v>
+      </c>
+      <c r="E320" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I320" s="34" t="s">
+        <v>533</v>
+      </c>
+      <c r="J320" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K320" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="321" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C321" s="34" t="s">
+        <v>534</v>
+      </c>
+      <c r="E321" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I321" s="34" t="s">
+        <v>534</v>
+      </c>
+      <c r="J321" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K321" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="322" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C322" s="36" t="s">
+        <v>535</v>
+      </c>
+      <c r="E322" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I322" s="36" t="s">
+        <v>535</v>
+      </c>
+      <c r="J322" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K322" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="323" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C323" s="36" t="s">
+        <v>536</v>
+      </c>
+      <c r="E323" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I323" s="36" t="s">
+        <v>536</v>
+      </c>
+      <c r="J323" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="K323" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="324" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C324" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="E324" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I324" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="J324" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K324" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="325" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C325" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="E325" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I325" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="J325" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K325" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="326" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C326" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="E326" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I326" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="J326" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K326" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="327" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C327" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="E327" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I327" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="J327" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K327" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="328" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C328" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="E328" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I328" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="J328" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K328" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="329" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C329" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="E329" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I329" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="J329" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K329" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="330" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C330" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="E330" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I330" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="J330" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K330" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="331" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C331" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="E331" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I331" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="J331" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K331" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="332" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C332" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="E332" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I332" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="J332" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K332" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="333" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C333" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="E333" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="I333" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="J333" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K333" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="334" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C334" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="E334" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I334" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="J334" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="K334" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="335" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C335" s="34" t="s">
+        <v>550</v>
+      </c>
+      <c r="E335" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I335" s="34" t="s">
+        <v>550</v>
+      </c>
+      <c r="J335" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="K335" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="336" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C336" s="34" t="s">
+        <v>551</v>
+      </c>
+      <c r="E336" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I336" s="34" t="s">
+        <v>551</v>
+      </c>
+      <c r="J336" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="K336" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="337" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C337" s="34" t="s">
+        <v>552</v>
+      </c>
+      <c r="E337" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I337" s="34" t="s">
+        <v>552</v>
+      </c>
+      <c r="J337" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="K337" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="338" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C338" s="34" t="s">
+        <v>553</v>
+      </c>
+      <c r="E338" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I338" s="34" t="s">
+        <v>553</v>
+      </c>
+      <c r="J338" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="K338" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="339" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C339" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="E339" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I339" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="J339" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K339" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="340" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C340" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="E340" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I340" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="J340" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K340" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="341" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C341" s="34" t="s">
+        <v>555</v>
+      </c>
+      <c r="E341" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I341" s="34" t="s">
+        <v>555</v>
+      </c>
+      <c r="J341" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K341" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="342" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C342" s="35" t="s">
+        <v>556</v>
+      </c>
+      <c r="E342" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I342" s="35" t="s">
+        <v>556</v>
+      </c>
+      <c r="J342" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K342" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="343" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C343" s="35" t="s">
+        <v>557</v>
+      </c>
+      <c r="E343" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I343" s="35" t="s">
+        <v>557</v>
+      </c>
+      <c r="J343" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K343" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="344" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C344" s="35" t="s">
+        <v>558</v>
+      </c>
+      <c r="E344" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I344" s="35" t="s">
+        <v>558</v>
+      </c>
+      <c r="J344" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K344" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="345" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C345" t="s">
+        <v>560</v>
+      </c>
+      <c r="E345" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I345" t="s">
+        <v>560</v>
+      </c>
+      <c r="J345" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K345" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P72">
     <sortCondition ref="E11:E72"/>
   </sortState>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="C2">
+    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C4">
+    <cfRule type="duplicateValues" dxfId="32" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
     <cfRule type="duplicateValues" dxfId="31" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C4">
-    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
-    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C6 C11 C13 C15 C17 C20 C23">
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C10">
+    <cfRule type="duplicateValues" dxfId="29" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
     <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C16">
     <cfRule type="duplicateValues" dxfId="26" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
+  <conditionalFormatting sqref="C18:C19">
     <cfRule type="duplicateValues" dxfId="25" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
+  <conditionalFormatting sqref="C21:C22">
     <cfRule type="duplicateValues" dxfId="24" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:C19">
-    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21:C22">
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C25">
-    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C29">
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30">
-    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
+    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39:C43">
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C44:C45">
     <cfRule type="duplicateValues" dxfId="18" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39:C43">
+  <conditionalFormatting sqref="C47:C52">
     <cfRule type="duplicateValues" dxfId="17" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C44:C45">
+  <conditionalFormatting sqref="C53">
     <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C52">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C53">
-    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C54:C55 C46">
-    <cfRule type="duplicateValues" dxfId="13" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C56:C57">
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C58:C59">
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C60:C62">
     <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C58:C59">
+  <conditionalFormatting sqref="C63">
     <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C60:C62">
+  <conditionalFormatting sqref="C65:C66">
     <cfRule type="duplicateValues" dxfId="10" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C63">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C65:C66">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C67 C64">
-    <cfRule type="duplicateValues" dxfId="7" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68:C69 C1 C24 C26:C27 C31 C33:C38 C41:C43 C72">
-    <cfRule type="duplicateValues" dxfId="6" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C70:C71">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C285:C344 C278:C279 C73:C276">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="duplicateValues" dxfId="3" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36">
-    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37">
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41:I42">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I285:I344 I278:I279 I73:I276">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inputs/location_code_crosswalk_CalSim.xlsx
+++ b/inputs/location_code_crosswalk_CalSim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/fnufferrodriguez_usbr_gov/Documents/Desktop/eis-appendix-generation/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{9BE2C0AE-041C-44F6-87C0-BC10225BA465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65FD36E7-F64C-4C54-913F-39C68A09D1D8}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{9BE2C0AE-041C-44F6-87C0-BC10225BA465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FEAA1EA-2EEE-4EF6-B9E6-9E6E55C16807}"/>
   <bookViews>
-    <workbookView xWindow="-33075" yWindow="840" windowWidth="27015" windowHeight="19365" xr2:uid="{14B88182-57F4-4B3C-8644-9F1A6EE53B53}"/>
+    <workbookView xWindow="-76920" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{14B88182-57F4-4B3C-8644-9F1A6EE53B53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="571">
   <si>
     <t>QueryID</t>
   </si>
@@ -1719,13 +1719,43 @@
   </si>
   <si>
     <t>D_SAC162_09_SA2</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PSC_N</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PRF_N</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PMI_N_WAMER</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PAG_N</t>
+  </si>
+  <si>
+    <t>SWP_FRSA</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PEX_S</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PRF_S</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PMI_S</t>
+  </si>
+  <si>
+    <t>DEL_CVP_PAG_S</t>
+  </si>
+  <si>
+    <t>DELIVERY-CVP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1791,8 +1821,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1841,8 +1877,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9D08E"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1881,13 +1923,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1999,6 +2052,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2344,10 +2402,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -2646,7 +2700,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E97D62-E007-4D94-B471-28936CBA853B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P345"/>
+  <dimension ref="A1:P354"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="26.41796875" customWidth="1"/>
@@ -10747,6 +10801,105 @@
         <v>86</v>
       </c>
       <c r="K345" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="346" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I346" s="41" t="s">
+        <v>561</v>
+      </c>
+      <c r="J346" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K346" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="347" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I347" s="42" t="s">
+        <v>562</v>
+      </c>
+      <c r="J347" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K347" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="348" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I348" s="42" t="s">
+        <v>563</v>
+      </c>
+      <c r="J348" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K348" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="349" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I349" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="J349" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K349" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="350" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I350" s="42" t="s">
+        <v>565</v>
+      </c>
+      <c r="J350" s="43" t="s">
+        <v>549</v>
+      </c>
+      <c r="K350" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="351" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I351" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="J351" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K351" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="352" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I352" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="J352" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K352" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="353" spans="9:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I353" s="42" t="s">
+        <v>568</v>
+      </c>
+      <c r="J353" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K353" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="354" spans="9:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="I354" s="42" t="s">
+        <v>569</v>
+      </c>
+      <c r="J354" s="43" t="s">
+        <v>570</v>
+      </c>
+      <c r="K354" s="11" t="s">
         <v>25</v>
       </c>
     </row>

--- a/inputs/location_code_crosswalk_CalSim.xlsx
+++ b/inputs/location_code_crosswalk_CalSim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/fnufferrodriguez_usbr_gov/Documents/Desktop/eis-appendix-generation/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\20251211_BA_Modeling_Appendix\EIS_Appendix_Generation\EIS-Appendix-Generation-main\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{9BE2C0AE-041C-44F6-87C0-BC10225BA465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FEAA1EA-2EEE-4EF6-B9E6-9E6E55C16807}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FE2963-74E0-4726-9550-B4F5513D770B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-76920" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{14B88182-57F4-4B3C-8644-9F1A6EE53B53}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{14B88182-57F4-4B3C-8644-9F1A6EE53B53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1940,7 +1940,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2054,9 +2054,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2701,21 +2698,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E97D62-E007-4D94-B471-28936CBA853B}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P354"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.41796875" customWidth="1"/>
-    <col min="3" max="3" width="60.41796875" customWidth="1"/>
-    <col min="4" max="4" width="22.41796875" customWidth="1"/>
-    <col min="5" max="5" width="16.83984375" customWidth="1"/>
-    <col min="6" max="6" width="21.578125" customWidth="1"/>
-    <col min="7" max="7" width="32.15625" customWidth="1"/>
-    <col min="8" max="8" width="16.26171875" customWidth="1"/>
-    <col min="9" max="10" width="20.68359375" customWidth="1"/>
-    <col min="11" max="11" width="32.26171875" customWidth="1"/>
-    <col min="13" max="13" width="22.68359375" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="3" width="60.44140625" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" customWidth="1"/>
+    <col min="7" max="7" width="32.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" customWidth="1"/>
+    <col min="9" max="10" width="20.6640625" customWidth="1"/>
+    <col min="11" max="11" width="32.21875" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2765,7 +2762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>74</v>
       </c>
@@ -2812,7 +2809,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>46</v>
       </c>
@@ -2859,7 +2856,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>98</v>
       </c>
@@ -2907,7 +2904,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>46</v>
       </c>
@@ -2954,7 +2951,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>104</v>
       </c>
@@ -3002,7 +2999,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>46</v>
       </c>
@@ -3049,7 +3046,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>46</v>
       </c>
@@ -3096,7 +3093,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>46</v>
       </c>
@@ -3143,7 +3140,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>94</v>
       </c>
@@ -3191,7 +3188,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>108</v>
       </c>
@@ -3239,7 +3236,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>74</v>
       </c>
@@ -3286,7 +3283,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>74</v>
       </c>
@@ -3333,7 +3330,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>131</v>
       </c>
@@ -3381,7 +3378,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>135</v>
       </c>
@@ -3429,7 +3426,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>189</v>
       </c>
@@ -3477,7 +3474,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>145</v>
       </c>
@@ -3525,7 +3522,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>185</v>
       </c>
@@ -3573,7 +3570,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>257</v>
       </c>
@@ -3621,7 +3618,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>243</v>
       </c>
@@ -3669,7 +3666,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>229</v>
       </c>
@@ -3717,7 +3714,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>282</v>
       </c>
@@ -3765,7 +3762,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>275</v>
       </c>
@@ -3813,7 +3810,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>32</v>
       </c>
@@ -3861,7 +3858,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>268</v>
       </c>
@@ -3909,7 +3906,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>223</v>
       </c>
@@ -3957,7 +3954,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>249</v>
       </c>
@@ -4005,7 +4002,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>245</v>
       </c>
@@ -4053,7 +4050,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>46</v>
       </c>
@@ -4100,7 +4097,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>260</v>
       </c>
@@ -4148,7 +4145,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>46</v>
       </c>
@@ -4195,7 +4192,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
         <v>87</v>
       </c>
@@ -4243,7 +4240,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>285</v>
       </c>
@@ -4291,7 +4288,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>235</v>
       </c>
@@ -4339,7 +4336,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>231</v>
       </c>
@@ -4387,7 +4384,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>46</v>
       </c>
@@ -4435,7 +4432,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>46</v>
       </c>
@@ -4482,7 +4479,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>46</v>
       </c>
@@ -4530,7 +4527,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>74</v>
       </c>
@@ -4577,7 +4574,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>69</v>
       </c>
@@ -4627,7 +4624,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>74</v>
       </c>
@@ -4675,7 +4672,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>201</v>
       </c>
@@ -4723,7 +4720,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>46</v>
       </c>
@@ -4771,7 +4768,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>213</v>
       </c>
@@ -4819,7 +4816,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
         <v>205</v>
       </c>
@@ -4867,7 +4864,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>38</v>
       </c>
@@ -4915,7 +4912,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="29" t="s">
         <v>209</v>
       </c>
@@ -4963,7 +4960,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>54</v>
       </c>
@@ -5011,7 +5008,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>197</v>
       </c>
@@ -5059,7 +5056,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>46</v>
       </c>
@@ -5107,7 +5104,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>58</v>
       </c>
@@ -5155,7 +5152,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>62</v>
       </c>
@@ -5203,7 +5200,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>165</v>
       </c>
@@ -5251,7 +5248,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>173</v>
       </c>
@@ -5299,7 +5296,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>169</v>
       </c>
@@ -5347,7 +5344,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>177</v>
       </c>
@@ -5395,7 +5392,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>181</v>
       </c>
@@ -5443,7 +5440,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>46</v>
       </c>
@@ -5491,7 +5488,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>253</v>
       </c>
@@ -5539,7 +5536,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>50</v>
       </c>
@@ -5587,7 +5584,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>77</v>
       </c>
@@ -5635,7 +5632,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>217</v>
       </c>
@@ -5683,7 +5680,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>239</v>
       </c>
@@ -5731,7 +5728,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>225</v>
       </c>
@@ -5779,7 +5776,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>278</v>
       </c>
@@ -5827,7 +5824,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>271</v>
       </c>
@@ -5875,7 +5872,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
         <v>120</v>
       </c>
@@ -5923,7 +5920,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>28</v>
       </c>
@@ -5971,7 +5968,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>16</v>
       </c>
@@ -6019,7 +6016,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>264</v>
       </c>
@@ -6067,7 +6064,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
         <v>193</v>
       </c>
@@ -6115,7 +6112,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
         <v>46</v>
       </c>
@@ -6163,7 +6160,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C73" s="34" t="s">
         <v>291</v>
       </c>
@@ -6180,7 +6177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C74" s="34" t="s">
         <v>292</v>
       </c>
@@ -6197,7 +6194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C75" s="34" t="s">
         <v>293</v>
       </c>
@@ -6214,7 +6211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C76" s="36" t="s">
         <v>294</v>
       </c>
@@ -6231,7 +6228,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C77" s="36" t="s">
         <v>295</v>
       </c>
@@ -6248,7 +6245,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C78" s="36" t="s">
         <v>296</v>
       </c>
@@ -6265,7 +6262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C79" s="36" t="s">
         <v>297</v>
       </c>
@@ -6282,7 +6279,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C80" s="36" t="s">
         <v>298</v>
       </c>
@@ -6299,7 +6296,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C81" s="36" t="s">
         <v>299</v>
       </c>
@@ -6316,7 +6313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C82" s="37" t="s">
         <v>300</v>
       </c>
@@ -6333,7 +6330,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C83" s="37" t="s">
         <v>301</v>
       </c>
@@ -6350,7 +6347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C84" s="36" t="s">
         <v>302</v>
       </c>
@@ -6367,7 +6364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C85" s="36" t="s">
         <v>303</v>
       </c>
@@ -6384,7 +6381,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C86" s="36" t="s">
         <v>305</v>
       </c>
@@ -6401,7 +6398,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C87" s="36" t="s">
         <v>306</v>
       </c>
@@ -6418,7 +6415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C88" s="34" t="s">
         <v>307</v>
       </c>
@@ -6435,7 +6432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C89" s="34" t="s">
         <v>308</v>
       </c>
@@ -6452,7 +6449,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C90" s="34" t="s">
         <v>309</v>
       </c>
@@ -6469,7 +6466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C91" s="34" t="s">
         <v>310</v>
       </c>
@@ -6486,7 +6483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C92" s="34" t="s">
         <v>311</v>
       </c>
@@ -6503,7 +6500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C93" s="34" t="s">
         <v>312</v>
       </c>
@@ -6520,7 +6517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C94" s="34" t="s">
         <v>313</v>
       </c>
@@ -6537,7 +6534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C95" s="34" t="s">
         <v>314</v>
       </c>
@@ -6554,7 +6551,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C96" s="34" t="s">
         <v>315</v>
       </c>
@@ -6571,7 +6568,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C97" s="34" t="s">
         <v>316</v>
       </c>
@@ -6588,7 +6585,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C98" s="34" t="s">
         <v>317</v>
       </c>
@@ -6605,7 +6602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C99" s="12" t="s">
         <v>318</v>
       </c>
@@ -6622,7 +6619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C100" s="34" t="s">
         <v>319</v>
       </c>
@@ -6639,7 +6636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C101" s="12" t="s">
         <v>320</v>
       </c>
@@ -6656,7 +6653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C102" s="34" t="s">
         <v>321</v>
       </c>
@@ -6673,7 +6670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C103" s="34" t="s">
         <v>322</v>
       </c>
@@ -6690,7 +6687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C104" s="34" t="s">
         <v>323</v>
       </c>
@@ -6707,7 +6704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C105" s="34" t="s">
         <v>324</v>
       </c>
@@ -6724,7 +6721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C106" s="34" t="s">
         <v>325</v>
       </c>
@@ -6741,7 +6738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C107" s="34" t="s">
         <v>326</v>
       </c>
@@ -6758,7 +6755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C108" s="34" t="s">
         <v>327</v>
       </c>
@@ -6775,7 +6772,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C109" s="34" t="s">
         <v>328</v>
       </c>
@@ -6792,7 +6789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C110" s="34" t="s">
         <v>329</v>
       </c>
@@ -6809,7 +6806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C111" s="34" t="s">
         <v>330</v>
       </c>
@@ -6826,7 +6823,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C112" s="34" t="s">
         <v>331</v>
       </c>
@@ -6843,7 +6840,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C113" s="34" t="s">
         <v>332</v>
       </c>
@@ -6860,7 +6857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C114" s="34" t="s">
         <v>333</v>
       </c>
@@ -6877,7 +6874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C115" s="34" t="s">
         <v>334</v>
       </c>
@@ -6894,7 +6891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C116" s="34" t="s">
         <v>335</v>
       </c>
@@ -6911,7 +6908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C117" s="34" t="s">
         <v>336</v>
       </c>
@@ -6928,7 +6925,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C118" s="34" t="s">
         <v>337</v>
       </c>
@@ -6945,7 +6942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C119" s="34" t="s">
         <v>338</v>
       </c>
@@ -6962,7 +6959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C120" s="34" t="s">
         <v>339</v>
       </c>
@@ -6979,7 +6976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C121" s="34" t="s">
         <v>340</v>
       </c>
@@ -6996,7 +6993,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C122" s="34" t="s">
         <v>341</v>
       </c>
@@ -7013,7 +7010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C123" s="34" t="s">
         <v>342</v>
       </c>
@@ -7030,7 +7027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C124" s="34" t="s">
         <v>343</v>
       </c>
@@ -7047,7 +7044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C125" s="34" t="s">
         <v>344</v>
       </c>
@@ -7064,7 +7061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C126" s="34" t="s">
         <v>345</v>
       </c>
@@ -7081,7 +7078,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C127" s="34" t="s">
         <v>346</v>
       </c>
@@ -7098,7 +7095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C128" s="34" t="s">
         <v>559</v>
       </c>
@@ -7115,7 +7112,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C129" s="34" t="s">
         <v>347</v>
       </c>
@@ -7132,7 +7129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C130" s="34" t="s">
         <v>348</v>
       </c>
@@ -7149,7 +7146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C131" s="34" t="s">
         <v>349</v>
       </c>
@@ -7166,7 +7163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C132" s="34" t="s">
         <v>350</v>
       </c>
@@ -7183,7 +7180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C133" s="34" t="s">
         <v>351</v>
       </c>
@@ -7200,7 +7197,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C134" s="34" t="s">
         <v>352</v>
       </c>
@@ -7217,7 +7214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C135" s="34" t="s">
         <v>353</v>
       </c>
@@ -7234,7 +7231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C136" s="34" t="s">
         <v>354</v>
       </c>
@@ -7251,7 +7248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C137" s="34" t="s">
         <v>355</v>
       </c>
@@ -7268,7 +7265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C138" s="34" t="s">
         <v>356</v>
       </c>
@@ -7285,7 +7282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C139" s="34" t="s">
         <v>357</v>
       </c>
@@ -7302,7 +7299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C140" s="34" t="s">
         <v>358</v>
       </c>
@@ -7319,7 +7316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C141" s="34" t="s">
         <v>359</v>
       </c>
@@ -7336,7 +7333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C142" s="34" t="s">
         <v>360</v>
       </c>
@@ -7353,7 +7350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C143" s="34" t="s">
         <v>361</v>
       </c>
@@ -7370,7 +7367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C144" s="34" t="s">
         <v>362</v>
       </c>
@@ -7387,7 +7384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C145" s="34" t="s">
         <v>363</v>
       </c>
@@ -7404,7 +7401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C146" s="34" t="s">
         <v>364</v>
       </c>
@@ -7421,7 +7418,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C147" s="34" t="s">
         <v>365</v>
       </c>
@@ -7438,7 +7435,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C148" s="34" t="s">
         <v>366</v>
       </c>
@@ -7455,7 +7452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C149" s="34" t="s">
         <v>367</v>
       </c>
@@ -7472,7 +7469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C150" s="34" t="s">
         <v>368</v>
       </c>
@@ -7489,7 +7486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C151" s="34" t="s">
         <v>369</v>
       </c>
@@ -7506,7 +7503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C152" s="34" t="s">
         <v>370</v>
       </c>
@@ -7523,7 +7520,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C153" s="36" t="s">
         <v>371</v>
       </c>
@@ -7540,7 +7537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C154" s="36" t="s">
         <v>372</v>
       </c>
@@ -7557,7 +7554,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C155" s="37" t="s">
         <v>373</v>
       </c>
@@ -7574,7 +7571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C156" s="37" t="s">
         <v>374</v>
       </c>
@@ -7591,7 +7588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C157" s="36" t="s">
         <v>375</v>
       </c>
@@ -7608,7 +7605,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C158" s="36" t="s">
         <v>376</v>
       </c>
@@ -7625,7 +7622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C159" s="36" t="s">
         <v>377</v>
       </c>
@@ -7642,7 +7639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C160" s="36" t="s">
         <v>378</v>
       </c>
@@ -7659,7 +7656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C161" s="36" t="s">
         <v>379</v>
       </c>
@@ -7676,7 +7673,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C162" s="36" t="s">
         <v>380</v>
       </c>
@@ -7693,7 +7690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C163" s="36" t="s">
         <v>381</v>
       </c>
@@ -7710,7 +7707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C164" s="34" t="s">
         <v>382</v>
       </c>
@@ -7727,7 +7724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C165" s="34" t="s">
         <v>384</v>
       </c>
@@ -7744,7 +7741,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C166" s="34" t="s">
         <v>385</v>
       </c>
@@ -7761,7 +7758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C167" s="34" t="s">
         <v>386</v>
       </c>
@@ -7778,7 +7775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C168" s="36" t="s">
         <v>387</v>
       </c>
@@ -7795,7 +7792,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C169" s="34" t="s">
         <v>388</v>
       </c>
@@ -7812,7 +7809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C170" s="34" t="s">
         <v>389</v>
       </c>
@@ -7829,7 +7826,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C171" s="34" t="s">
         <v>390</v>
       </c>
@@ -7846,7 +7843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C172" s="34" t="s">
         <v>391</v>
       </c>
@@ -7863,7 +7860,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C173" s="34" t="s">
         <v>392</v>
       </c>
@@ -7880,7 +7877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C174" s="34" t="s">
         <v>393</v>
       </c>
@@ -7897,7 +7894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C175" s="34" t="s">
         <v>394</v>
       </c>
@@ -7914,7 +7911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C176" s="34" t="s">
         <v>395</v>
       </c>
@@ -7931,7 +7928,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C177" s="34" t="s">
         <v>396</v>
       </c>
@@ -7948,7 +7945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C178" s="34" t="s">
         <v>397</v>
       </c>
@@ -7965,7 +7962,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C179" s="34" t="s">
         <v>398</v>
       </c>
@@ -7982,7 +7979,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="180" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C180" s="34" t="s">
         <v>399</v>
       </c>
@@ -7999,7 +7996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C181" s="34" t="s">
         <v>400</v>
       </c>
@@ -8016,7 +8013,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C182" s="34" t="s">
         <v>401</v>
       </c>
@@ -8033,7 +8030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="183" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C183" s="34" t="s">
         <v>402</v>
       </c>
@@ -8050,7 +8047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C184" s="34" t="s">
         <v>403</v>
       </c>
@@ -8067,7 +8064,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="185" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C185" s="34" t="s">
         <v>404</v>
       </c>
@@ -8084,7 +8081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C186" s="34" t="s">
         <v>405</v>
       </c>
@@ -8101,7 +8098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="187" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C187" s="34" t="s">
         <v>406</v>
       </c>
@@ -8118,7 +8115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C188" s="34" t="s">
         <v>407</v>
       </c>
@@ -8135,7 +8132,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C189" s="34" t="s">
         <v>408</v>
       </c>
@@ -8152,7 +8149,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C190" s="34" t="s">
         <v>409</v>
       </c>
@@ -8169,7 +8166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C191" s="34" t="s">
         <v>410</v>
       </c>
@@ -8186,7 +8183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C192" s="37" t="s">
         <v>411</v>
       </c>
@@ -8203,7 +8200,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C193" s="37" t="s">
         <v>412</v>
       </c>
@@ -8220,7 +8217,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C194" s="37" t="s">
         <v>413</v>
       </c>
@@ -8237,7 +8234,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="195" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C195" s="37" t="s">
         <v>414</v>
       </c>
@@ -8254,7 +8251,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C196" s="37" t="s">
         <v>415</v>
       </c>
@@ -8271,7 +8268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C197" s="36" t="s">
         <v>416</v>
       </c>
@@ -8288,7 +8285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C198" s="34" t="s">
         <v>417</v>
       </c>
@@ -8305,7 +8302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C199" s="34" t="s">
         <v>418</v>
       </c>
@@ -8322,7 +8319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C200" s="34" t="s">
         <v>419</v>
       </c>
@@ -8339,7 +8336,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C201" s="34" t="s">
         <v>420</v>
       </c>
@@ -8356,7 +8353,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C202" s="34" t="s">
         <v>421</v>
       </c>
@@ -8373,7 +8370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C203" s="34" t="s">
         <v>422</v>
       </c>
@@ -8390,7 +8387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="204" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C204" s="34" t="s">
         <v>423</v>
       </c>
@@ -8407,7 +8404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C205" s="34" t="s">
         <v>424</v>
       </c>
@@ -8424,7 +8421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C206" s="34" t="s">
         <v>425</v>
       </c>
@@ -8441,7 +8438,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C207" s="34" t="s">
         <v>426</v>
       </c>
@@ -8458,7 +8455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C208" s="36" t="s">
         <v>427</v>
       </c>
@@ -8475,7 +8472,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C209" s="36" t="s">
         <v>428</v>
       </c>
@@ -8492,7 +8489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C210" s="36" t="s">
         <v>429</v>
       </c>
@@ -8509,7 +8506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C211" s="36" t="s">
         <v>430</v>
       </c>
@@ -8526,7 +8523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="212" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C212" s="36" t="s">
         <v>431</v>
       </c>
@@ -8543,7 +8540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C213" s="36" t="s">
         <v>432</v>
       </c>
@@ -8560,7 +8557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C214" s="36" t="s">
         <v>433</v>
       </c>
@@ -8577,7 +8574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C215" s="37" t="s">
         <v>434</v>
       </c>
@@ -8594,7 +8591,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="216" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C216" s="37" t="s">
         <v>435</v>
       </c>
@@ -8611,7 +8608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C217" s="36" t="s">
         <v>436</v>
       </c>
@@ -8628,7 +8625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="218" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C218" s="37" t="s">
         <v>437</v>
       </c>
@@ -8645,7 +8642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C219" s="37" t="s">
         <v>438</v>
       </c>
@@ -8662,7 +8659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C220" s="34" t="s">
         <v>439</v>
       </c>
@@ -8679,7 +8676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="221" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C221" s="34" t="s">
         <v>440</v>
       </c>
@@ -8696,7 +8693,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C222" s="34" t="s">
         <v>441</v>
       </c>
@@ -8713,7 +8710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C223" s="34" t="s">
         <v>442</v>
       </c>
@@ -8730,7 +8727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="224" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C224" s="34" t="s">
         <v>443</v>
       </c>
@@ -8747,7 +8744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C225" s="34" t="s">
         <v>444</v>
       </c>
@@ -8764,7 +8761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C226" s="34" t="s">
         <v>445</v>
       </c>
@@ -8781,7 +8778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C227" s="34" t="s">
         <v>446</v>
       </c>
@@ -8798,7 +8795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C228" s="34" t="s">
         <v>447</v>
       </c>
@@ -8815,7 +8812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C229" s="34" t="s">
         <v>448</v>
       </c>
@@ -8832,7 +8829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C230" s="34" t="s">
         <v>449</v>
       </c>
@@ -8849,7 +8846,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C231" s="37" t="s">
         <v>450</v>
       </c>
@@ -8866,7 +8863,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C232" s="36" t="s">
         <v>451</v>
       </c>
@@ -8883,7 +8880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C233" s="36" t="s">
         <v>452</v>
       </c>
@@ -8900,7 +8897,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C234" s="34" t="s">
         <v>453</v>
       </c>
@@ -8917,7 +8914,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C235" s="34" t="s">
         <v>454</v>
       </c>
@@ -8934,7 +8931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C236" s="38" t="s">
         <v>455</v>
       </c>
@@ -8951,7 +8948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C237" s="34" t="s">
         <v>456</v>
       </c>
@@ -8968,7 +8965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C238" s="34" t="s">
         <v>457</v>
       </c>
@@ -8985,7 +8982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C239" s="38" t="s">
         <v>458</v>
       </c>
@@ -9002,7 +8999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C240" s="38" t="s">
         <v>459</v>
       </c>
@@ -9019,7 +9016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C241" s="38" t="s">
         <v>460</v>
       </c>
@@ -9036,7 +9033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C242" s="38" t="s">
         <v>461</v>
       </c>
@@ -9053,7 +9050,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C243" s="38" t="s">
         <v>462</v>
       </c>
@@ -9070,7 +9067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C244" s="34" t="s">
         <v>463</v>
       </c>
@@ -9087,7 +9084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C245" s="34" t="s">
         <v>464</v>
       </c>
@@ -9104,7 +9101,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C246" s="34" t="s">
         <v>465</v>
       </c>
@@ -9121,7 +9118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C247" s="39" t="s">
         <v>466</v>
       </c>
@@ -9138,7 +9135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C248" s="39" t="s">
         <v>467</v>
       </c>
@@ -9155,7 +9152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C249" s="39" t="s">
         <v>468</v>
       </c>
@@ -9172,7 +9169,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C250" s="34" t="s">
         <v>469</v>
       </c>
@@ -9189,7 +9186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C251" s="34" t="s">
         <v>470</v>
       </c>
@@ -9206,7 +9203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C252" s="34" t="s">
         <v>471</v>
       </c>
@@ -9223,7 +9220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="253" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C253" s="34" t="s">
         <v>472</v>
       </c>
@@ -9240,7 +9237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C254" s="34" t="s">
         <v>473</v>
       </c>
@@ -9257,7 +9254,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C255" s="34" t="s">
         <v>474</v>
       </c>
@@ -9274,7 +9271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="256" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C256" s="34" t="s">
         <v>475</v>
       </c>
@@ -9291,7 +9288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C257" s="34" t="s">
         <v>476</v>
       </c>
@@ -9308,7 +9305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="258" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C258" s="34" t="s">
         <v>477</v>
       </c>
@@ -9325,7 +9322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C259" s="34" t="s">
         <v>478</v>
       </c>
@@ -9342,7 +9339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C260" s="34" t="s">
         <v>479</v>
       </c>
@@ -9359,7 +9356,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C261" s="34" t="s">
         <v>480</v>
       </c>
@@ -9376,7 +9373,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C262" s="38" t="s">
         <v>481</v>
       </c>
@@ -9393,7 +9390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C263" s="38" t="s">
         <v>482</v>
       </c>
@@ -9410,7 +9407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C264" s="38" t="s">
         <v>483</v>
       </c>
@@ -9427,7 +9424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C265" s="38" t="s">
         <v>484</v>
       </c>
@@ -9444,7 +9441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C266" s="34" t="s">
         <v>485</v>
       </c>
@@ -9461,7 +9458,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="267" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C267" s="38" t="s">
         <v>486</v>
       </c>
@@ -9478,7 +9475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C268" s="40" t="s">
         <v>487</v>
       </c>
@@ -9495,7 +9492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C269" s="40" t="s">
         <v>488</v>
       </c>
@@ -9512,7 +9509,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="270" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C270" s="40" t="s">
         <v>489</v>
       </c>
@@ -9529,7 +9526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C271" s="38" t="s">
         <v>490</v>
       </c>
@@ -9546,7 +9543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="272" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C272" s="40" t="s">
         <v>491</v>
       </c>
@@ -9563,7 +9560,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="273" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C273" s="40" t="s">
         <v>492</v>
       </c>
@@ -9580,7 +9577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="274" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C274" s="34" t="s">
         <v>493</v>
       </c>
@@ -9597,7 +9594,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="275" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C275" s="34" t="s">
         <v>494</v>
       </c>
@@ -9614,7 +9611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="276" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C276" s="34" t="s">
         <v>495</v>
       </c>
@@ -9631,7 +9628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="277" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C277" s="34" t="s">
         <v>352</v>
       </c>
@@ -9648,7 +9645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C278" s="34" t="s">
         <v>496</v>
       </c>
@@ -9665,7 +9662,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="279" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C279" s="34" t="s">
         <v>497</v>
       </c>
@@ -9682,7 +9679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C280" s="34" t="s">
         <v>354</v>
       </c>
@@ -9699,7 +9696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="281" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C281" s="34" t="s">
         <v>355</v>
       </c>
@@ -9716,7 +9713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="282" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C282" s="34" t="s">
         <v>353</v>
       </c>
@@ -9733,7 +9730,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="283" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C283" s="34" t="s">
         <v>356</v>
       </c>
@@ -9750,7 +9747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C284" s="34" t="s">
         <v>357</v>
       </c>
@@ -9767,7 +9764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="285" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C285" s="34" t="s">
         <v>498</v>
       </c>
@@ -9784,7 +9781,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="286" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C286" s="34" t="s">
         <v>499</v>
       </c>
@@ -9801,7 +9798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="287" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C287" s="34" t="s">
         <v>500</v>
       </c>
@@ -9818,7 +9815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="288" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C288" s="34" t="s">
         <v>501</v>
       </c>
@@ -9835,7 +9832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C289" s="34" t="s">
         <v>502</v>
       </c>
@@ -9852,7 +9849,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="290" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C290" s="34" t="s">
         <v>503</v>
       </c>
@@ -9869,7 +9866,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="291" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C291" s="34" t="s">
         <v>504</v>
       </c>
@@ -9886,7 +9883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="292" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C292" s="34" t="s">
         <v>505</v>
       </c>
@@ -9903,7 +9900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="293" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C293" s="34" t="s">
         <v>506</v>
       </c>
@@ -9920,7 +9917,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="294" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C294" s="34" t="s">
         <v>507</v>
       </c>
@@ -9937,7 +9934,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="295" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C295" s="34" t="s">
         <v>508</v>
       </c>
@@ -9954,7 +9951,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C296" s="34" t="s">
         <v>509</v>
       </c>
@@ -9971,7 +9968,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="297" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C297" s="34" t="s">
         <v>510</v>
       </c>
@@ -9988,7 +9985,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="298" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C298" s="34" t="s">
         <v>511</v>
       </c>
@@ -10005,7 +10002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="299" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C299" s="34" t="s">
         <v>512</v>
       </c>
@@ -10022,7 +10019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="300" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C300" s="34" t="s">
         <v>513</v>
       </c>
@@ -10039,7 +10036,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="301" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C301" s="34" t="s">
         <v>514</v>
       </c>
@@ -10056,7 +10053,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="302" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C302" s="34" t="s">
         <v>515</v>
       </c>
@@ -10073,7 +10070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C303" s="34" t="s">
         <v>516</v>
       </c>
@@ -10090,7 +10087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="304" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C304" s="34" t="s">
         <v>517</v>
       </c>
@@ -10107,7 +10104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="305" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C305" s="34" t="s">
         <v>518</v>
       </c>
@@ -10124,7 +10121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="306" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C306" s="34" t="s">
         <v>519</v>
       </c>
@@ -10141,7 +10138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="307" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C307" s="34" t="s">
         <v>520</v>
       </c>
@@ -10158,7 +10155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="308" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C308" s="34" t="s">
         <v>521</v>
       </c>
@@ -10175,7 +10172,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="309" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C309" s="34" t="s">
         <v>522</v>
       </c>
@@ -10192,7 +10189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C310" s="34" t="s">
         <v>523</v>
       </c>
@@ -10209,7 +10206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="311" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C311" s="34" t="s">
         <v>524</v>
       </c>
@@ -10226,7 +10223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="312" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C312" s="34" t="s">
         <v>525</v>
       </c>
@@ -10243,7 +10240,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="313" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C313" s="34" t="s">
         <v>526</v>
       </c>
@@ -10260,7 +10257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="314" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C314" s="34" t="s">
         <v>527</v>
       </c>
@@ -10277,7 +10274,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="315" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C315" s="34" t="s">
         <v>528</v>
       </c>
@@ -10294,7 +10291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="316" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C316" s="34" t="s">
         <v>529</v>
       </c>
@@ -10311,7 +10308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="317" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C317" s="34" t="s">
         <v>530</v>
       </c>
@@ -10328,7 +10325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="318" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C318" s="34" t="s">
         <v>531</v>
       </c>
@@ -10345,7 +10342,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C319" s="34" t="s">
         <v>532</v>
       </c>
@@ -10362,7 +10359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="320" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="320" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C320" s="34" t="s">
         <v>533</v>
       </c>
@@ -10379,7 +10376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="321" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="321" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C321" s="34" t="s">
         <v>534</v>
       </c>
@@ -10396,7 +10393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="322" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C322" s="36" t="s">
         <v>535</v>
       </c>
@@ -10413,7 +10410,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="323" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="323" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C323" s="36" t="s">
         <v>536</v>
       </c>
@@ -10430,7 +10427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="324" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C324" s="34" t="s">
         <v>537</v>
       </c>
@@ -10447,7 +10444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="325" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C325" s="34" t="s">
         <v>539</v>
       </c>
@@ -10464,7 +10461,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="326" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C326" s="34" t="s">
         <v>540</v>
       </c>
@@ -10481,7 +10478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C327" s="34" t="s">
         <v>541</v>
       </c>
@@ -10498,7 +10495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="328" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C328" s="34" t="s">
         <v>542</v>
       </c>
@@ -10515,7 +10512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="329" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C329" s="34" t="s">
         <v>543</v>
       </c>
@@ -10532,7 +10529,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C330" s="34" t="s">
         <v>544</v>
       </c>
@@ -10549,7 +10546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C331" s="34" t="s">
         <v>545</v>
       </c>
@@ -10566,7 +10563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="332" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C332" s="34" t="s">
         <v>546</v>
       </c>
@@ -10583,7 +10580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="333" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C333" s="34" t="s">
         <v>547</v>
       </c>
@@ -10600,7 +10597,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="334" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C334" s="34" t="s">
         <v>548</v>
       </c>
@@ -10617,7 +10614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="335" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C335" s="34" t="s">
         <v>550</v>
       </c>
@@ -10634,7 +10631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="336" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C336" s="34" t="s">
         <v>551</v>
       </c>
@@ -10651,7 +10648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="337" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="337" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C337" s="34" t="s">
         <v>552</v>
       </c>
@@ -10668,7 +10665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="338" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C338" s="34" t="s">
         <v>553</v>
       </c>
@@ -10685,7 +10682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="339" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C339" s="34" t="s">
         <v>110</v>
       </c>
@@ -10702,7 +10699,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C340" s="34" t="s">
         <v>554</v>
       </c>
@@ -10719,7 +10716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C341" s="34" t="s">
         <v>555</v>
       </c>
@@ -10736,7 +10733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C342" s="35" t="s">
         <v>556</v>
       </c>
@@ -10753,7 +10750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="343" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C343" s="35" t="s">
         <v>557</v>
       </c>
@@ -10770,7 +10767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C344" s="35" t="s">
         <v>558</v>
       </c>
@@ -10787,7 +10784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C345" t="s">
         <v>560</v>
       </c>
@@ -10804,99 +10801,99 @@
         <v>25</v>
       </c>
     </row>
-    <row r="346" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I346" s="41" t="s">
         <v>561</v>
       </c>
-      <c r="J346" s="43" t="s">
+      <c r="J346" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K346" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="347" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I347" s="42" t="s">
         <v>562</v>
       </c>
-      <c r="J347" s="43" t="s">
+      <c r="J347" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K347" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="348" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I348" s="42" t="s">
         <v>563</v>
       </c>
-      <c r="J348" s="43" t="s">
+      <c r="J348" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K348" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="349" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I349" s="42" t="s">
         <v>564</v>
       </c>
-      <c r="J349" s="43" t="s">
+      <c r="J349" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K349" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I350" s="42" t="s">
         <v>565</v>
       </c>
-      <c r="J350" s="43" t="s">
+      <c r="J350" s="35" t="s">
         <v>549</v>
       </c>
       <c r="K350" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="351" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I351" s="42" t="s">
         <v>566</v>
       </c>
-      <c r="J351" s="43" t="s">
+      <c r="J351" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K351" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="352" spans="3:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I352" s="42" t="s">
         <v>567</v>
       </c>
-      <c r="J352" s="43" t="s">
+      <c r="J352" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K352" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="353" spans="9:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I353" s="42" t="s">
         <v>568</v>
       </c>
-      <c r="J353" s="43" t="s">
+      <c r="J353" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K353" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="9:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="354" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I354" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="J354" s="43" t="s">
+      <c r="J354" s="35" t="s">
         <v>570</v>
       </c>
       <c r="K354" s="11" t="s">
